--- a/public/testStock.xlsx
+++ b/public/testStock.xlsx
@@ -139,7 +139,7 @@
     <t xml:space="preserve">11/12/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">DIVIDENDE 215 AMUNDI NYS.AR.GOL</t>
+    <t xml:space="preserve">DIVIDENDE 215 AMUNDI NYS.AR.GOLD</t>
   </si>
   <si>
     <t xml:space="preserve">ACHAT 1060 VAN.CR.BL.IN.USD-A</t>
@@ -580,7 +580,7 @@
     <t xml:space="preserve">03/05/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">DIVIDENDE. 340 STELLANTIS</t>
+    <t xml:space="preserve">DIVIDENDE 340 STELLANTIS</t>
   </si>
   <si>
     <t xml:space="preserve">29/04/2024</t>
@@ -918,16 +918,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1086,10 +1082,10 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>-5997.48</v>
       </c>
     </row>
@@ -1097,10 +1093,10 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>9474.63</v>
       </c>
     </row>
@@ -1108,10 +1104,10 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>10113.67</v>
       </c>
     </row>
@@ -1119,10 +1115,10 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>-9040.54</v>
       </c>
     </row>
@@ -1130,10 +1126,10 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>-6283.21</v>
       </c>
     </row>
@@ -1141,15 +1137,15 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>-17891.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1160,7 +1156,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1171,7 +1167,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1182,7 +1178,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1193,7 +1189,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1204,7 +1200,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1215,7 +1211,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1226,7 +1222,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1237,7 +1233,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1248,7 +1244,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1259,7 +1255,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1270,7 +1266,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1281,7 +1277,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1292,7 +1288,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1303,7 +1299,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1314,7 +1310,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1325,7 +1321,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1336,7 +1332,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1347,7 +1343,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1358,7 +1354,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1369,7 +1365,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1380,7 +1376,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1391,7 +1387,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1402,7 +1398,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1413,7 +1409,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1424,7 +1420,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1435,7 +1431,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1446,7 +1442,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -1457,7 +1453,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -1468,7 +1464,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -1479,7 +1475,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1490,7 +1486,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -1501,7 +1497,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -1512,7 +1508,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1523,7 +1519,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -1534,7 +1530,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -1545,7 +1541,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -1556,7 +1552,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -1567,7 +1563,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -1578,7 +1574,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -1589,7 +1585,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -1600,7 +1596,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -1611,7 +1607,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -1622,7 +1618,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1633,7 +1629,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -1644,7 +1640,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -1655,7 +1651,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -1666,7 +1662,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -1677,7 +1673,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -1688,7 +1684,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -1699,7 +1695,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -1710,7 +1706,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -1721,7 +1717,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -1732,7 +1728,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -1743,7 +1739,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -1754,7 +1750,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -1765,7 +1761,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -1776,7 +1772,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -1787,7 +1783,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -1798,7 +1794,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -1809,7 +1805,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -1820,7 +1816,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -1831,7 +1827,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -1842,7 +1838,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -1853,7 +1849,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -1864,7 +1860,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -1875,7 +1871,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -1886,7 +1882,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -1897,7 +1893,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -1908,7 +1904,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -1919,7 +1915,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -1930,7 +1926,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -1941,7 +1937,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -1952,7 +1948,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -1963,7 +1959,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -1974,7 +1970,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -1985,7 +1981,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -1996,7 +1992,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -2007,7 +2003,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -2018,7 +2014,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -2029,7 +2025,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -2040,7 +2036,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -2051,7 +2047,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -2062,7 +2058,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -2073,7 +2069,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -2084,7 +2080,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>125</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -2095,7 +2091,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -2106,7 +2102,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -2117,7 +2113,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -2128,7 +2124,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -2139,7 +2135,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -2150,7 +2146,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -2161,7 +2157,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -2172,7 +2168,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -2183,7 +2179,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -2194,7 +2190,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -2205,7 +2201,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -2216,7 +2212,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -2227,7 +2223,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="3" t="s">
         <v>141</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -2238,7 +2234,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="3" t="s">
         <v>141</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -2249,7 +2245,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -2260,7 +2256,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -2271,7 +2267,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -2282,7 +2278,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -2293,7 +2289,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -2304,7 +2300,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -2315,7 +2311,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -2326,7 +2322,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -2337,7 +2333,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>147</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -2348,7 +2344,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -2359,7 +2355,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="3" t="s">
         <v>149</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -2370,7 +2366,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -2381,7 +2377,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -2392,7 +2388,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -2403,7 +2399,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -2414,7 +2410,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -2425,7 +2421,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -2436,7 +2432,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -2447,7 +2443,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -2458,7 +2454,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="3" t="s">
         <v>156</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -2469,7 +2465,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="3" t="s">
         <v>156</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -2480,7 +2476,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="3" t="s">
         <v>158</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -2491,7 +2487,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="3" t="s">
         <v>159</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -2502,7 +2498,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -2513,7 +2509,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -2524,7 +2520,7 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -2535,7 +2531,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -2546,7 +2542,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="3" t="s">
         <v>165</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -2557,7 +2553,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -2568,7 +2564,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -2579,7 +2575,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -2590,7 +2586,7 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -2601,7 +2597,7 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -2612,7 +2608,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -2623,7 +2619,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -2634,7 +2630,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="3" t="s">
         <v>177</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -2645,7 +2641,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -2656,7 +2652,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="3" t="s">
         <v>181</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -2667,7 +2663,7 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="3" t="s">
         <v>182</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -2678,7 +2674,7 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="3" t="s">
         <v>183</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -2689,7 +2685,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -2700,7 +2696,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -2711,7 +2707,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -2722,7 +2718,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -2733,7 +2729,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -2744,7 +2740,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="3" t="s">
         <v>191</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -2755,7 +2751,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -2766,7 +2762,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -2777,7 +2773,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="3" t="s">
         <v>194</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -2788,7 +2784,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="3" t="s">
         <v>196</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -2799,7 +2795,7 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -2810,7 +2806,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="3" t="s">
         <v>198</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -2821,7 +2817,7 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -2832,7 +2828,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="3" t="s">
         <v>200</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -2843,7 +2839,7 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -2854,7 +2850,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -2865,7 +2861,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -2876,7 +2872,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B165" s="1" t="s">
@@ -2887,7 +2883,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -2898,7 +2894,7 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -2909,7 +2905,7 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -2920,7 +2916,7 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="3" t="s">
         <v>209</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -2931,7 +2927,7 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -2942,7 +2938,7 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -2953,7 +2949,7 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -2964,7 +2960,7 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -2975,7 +2971,7 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="3" t="s">
         <v>215</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -2986,7 +2982,7 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="3" t="s">
         <v>217</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -2997,7 +2993,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -3008,7 +3004,7 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -3019,7 +3015,7 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -3030,7 +3026,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -3041,7 +3037,7 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -3052,7 +3048,7 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>224</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -3063,7 +3059,7 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -3074,7 +3070,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="3" t="s">
         <v>226</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -3085,7 +3081,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="3" t="s">
         <v>228</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -3096,7 +3092,7 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -3107,7 +3103,7 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -3118,7 +3114,7 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="4" t="s">
+      <c r="A187" s="3" t="s">
         <v>232</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -3129,7 +3125,7 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="3" t="s">
         <v>232</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -3140,7 +3136,7 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="4" t="s">
+      <c r="A189" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -3151,7 +3147,7 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="3" t="s">
         <v>236</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -3162,7 +3158,7 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="3" t="s">
         <v>238</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -3173,7 +3169,7 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -3184,7 +3180,7 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="4" t="s">
+      <c r="A193" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -3195,7 +3191,7 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="3" t="s">
         <v>241</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -3206,7 +3202,7 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="4" t="s">
+      <c r="A195" s="3" t="s">
         <v>242</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -3217,7 +3213,7 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="3" t="s">
         <v>244</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -3228,7 +3224,7 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="4" t="s">
+      <c r="A197" s="3" t="s">
         <v>244</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -3239,7 +3235,7 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -3250,7 +3246,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="4" t="s">
+      <c r="A199" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -3261,7 +3257,7 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="4" t="s">
+      <c r="A200" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -3272,7 +3268,7 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="4" t="s">
+      <c r="A201" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -3283,7 +3279,7 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -3294,7 +3290,7 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="4" t="s">
+      <c r="A203" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -3305,7 +3301,7 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="4" t="s">
+      <c r="A204" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -3316,7 +3312,7 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="4" t="s">
+      <c r="A205" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -3327,7 +3323,7 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -3338,7 +3334,7 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -3349,7 +3345,7 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B208" s="1" t="s">
@@ -3360,7 +3356,7 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -3371,7 +3367,7 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B210" s="1" t="s">
@@ -3382,7 +3378,7 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -3393,7 +3389,7 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="3" t="s">
         <v>259</v>
       </c>
       <c r="B212" s="1" t="s">
@@ -3404,7 +3400,7 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="4" t="s">
+      <c r="A213" s="3" t="s">
         <v>261</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -3415,7 +3411,7 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B214" s="1" t="s">
@@ -3426,7 +3422,7 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -3437,7 +3433,7 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B216" s="1" t="s">
@@ -3448,7 +3444,7 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="4" t="s">
+      <c r="A217" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B217" s="1" t="s">
@@ -3459,7 +3455,7 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="4" t="s">
+      <c r="A218" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B218" s="1" t="s">
@@ -3470,7 +3466,7 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="4" t="s">
+      <c r="A219" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B219" s="1" t="s">
@@ -3481,7 +3477,7 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B220" s="1" t="s">
@@ -3492,7 +3488,7 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="4" t="s">
+      <c r="A221" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B221" s="1" t="s">
@@ -3503,7 +3499,7 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B222" s="1" t="s">
@@ -3514,7 +3510,7 @@
       </c>
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="4" t="s">
+      <c r="A223" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B223" s="1" t="s">
@@ -3525,7 +3521,7 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B224" s="1" t="s">
@@ -3536,7 +3532,7 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="4" t="s">
+      <c r="A225" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B225" s="1" t="s">
